--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/biobio.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/biobio.xlsx
@@ -28122,7 +28122,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/biobio.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M434"/>
+  <dimension ref="A1:M446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1944,7 +1944,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057418-98-CM25</t>
+          <t>1057540-6539-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.607.302-8</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE MULCHEN</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>20064.79</v>
+        <v>72179.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057540-6539-CM25</t>
+          <t>1057418-98-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.607.302-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE MULCHEN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>72179.67</v>
+        <v>20064.79</v>
       </c>
     </row>
     <row r="26">
@@ -2204,7 +2204,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057415-55-CM25</t>
+          <t>1057422-92-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>28244.85</v>
+        <v>18381.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057422-92-CM25</t>
+          <t>1057415-55-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>18381.3</v>
+        <v>28244.85</v>
       </c>
     </row>
     <row r="30">
@@ -2854,7 +2854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2421-2813-CM25</t>
+          <t>654-58-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2874,17 +2874,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5236.54</v>
+        <v>3098.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>654-58-CM25</t>
+          <t>2421-2813-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2939,17 +2939,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3098.66</v>
+        <v>5236.54</v>
       </c>
     </row>
     <row r="40">
@@ -3179,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3365-42-CM25</t>
+          <t>1057422-142-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3221.89</v>
+        <v>16523.41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057422-142-CM25</t>
+          <t>3365-42-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16523.41</v>
+        <v>3221.89</v>
       </c>
     </row>
     <row r="45">
@@ -3439,7 +3439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3355-87-CM25</t>
+          <t>3355-94-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1276.95</v>
+        <v>2127.21</v>
       </c>
     </row>
     <row r="48">
@@ -3569,7 +3569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3355-94-CM25</t>
+          <t>3355-87-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2127.21</v>
+        <v>1276.95</v>
       </c>
     </row>
     <row r="50">
@@ -3699,7 +3699,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>554892-3-CM25</t>
+          <t>1057420-236-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>261.74</v>
+        <v>18133.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057420-236-CM25</t>
+          <t>554892-3-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>18133.18</v>
+        <v>261.74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1576-41-CM25</t>
+          <t>1576-40-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8549.129999999999</v>
+        <v>58289.53</v>
       </c>
     </row>
     <row r="54">
@@ -3959,7 +3959,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1576-40-CM25</t>
+          <t>1576-41-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>58289.53</v>
+        <v>8549.129999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4934,7 +4934,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3355-146-CM25</t>
+          <t>1057420-316-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1238.12</v>
+        <v>17981.61</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057420-316-CM25</t>
+          <t>3355-146-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>17981.61</v>
+        <v>1238.12</v>
       </c>
     </row>
     <row r="72">
@@ -5389,7 +5389,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2102-371-CM25</t>
+          <t>652-145-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>25372.55</v>
+        <v>32973.85</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>652-145-CM25</t>
+          <t>2102-371-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>32973.85</v>
+        <v>25372.55</v>
       </c>
     </row>
     <row r="79">
@@ -5844,7 +5844,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>831-96-CM25</t>
+          <t>4359-123-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5864,17 +5864,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1835.54</v>
+        <v>2490.83</v>
       </c>
     </row>
     <row r="85">
@@ -5974,7 +5974,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4359-123-CM25</t>
+          <t>831-96-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5994,17 +5994,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2490.83</v>
+        <v>1835.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4362-24-CM25</t>
+          <t>1057541-409-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>20781.98</v>
+        <v>2018.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057541-409-CM25</t>
+          <t>4362-24-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2018.66</v>
+        <v>20781.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4414-594-CM25</t>
+          <t>3365-85-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>13964.29</v>
+        <v>3214.54</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057422-310-CM25</t>
+          <t>3361-32-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>20556.63</v>
+        <v>642.91</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3361-32-CM25</t>
+          <t>1057415-218-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>642.91</v>
+        <v>24430.49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3365-85-CM25</t>
+          <t>4414-594-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3214.54</v>
+        <v>13964.29</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057415-218-CM25</t>
+          <t>1057422-310-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>24430.49</v>
+        <v>20556.63</v>
       </c>
     </row>
     <row r="94">
@@ -6559,7 +6559,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>995118-60-CM25</t>
+          <t>1057414-284-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4854.01</v>
+        <v>340.63</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2101-2369-CM25</t>
+          <t>1057420-416-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.213-k</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL INTERCULTURAL KALLVU LLANKA.-</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5254.23</v>
+        <v>20554.7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1057420-416-CM25</t>
+          <t>2101-2369-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.602.213-k</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>HOSPITAL INTERCULTURAL KALLVU LLANKA.-</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>20554.7</v>
+        <v>5254.23</v>
       </c>
     </row>
     <row r="98">
@@ -6819,7 +6819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057414-284-CM25</t>
+          <t>995118-60-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>340.63</v>
+        <v>4854.01</v>
       </c>
     </row>
     <row r="100">
@@ -7014,7 +7014,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3319-105-CM25</t>
+          <t>4358-140-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>48041.51</v>
+        <v>6315.87</v>
       </c>
     </row>
     <row r="103">
@@ -7144,7 +7144,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4358-140-CM25</t>
+          <t>3319-105-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>6315.87</v>
+        <v>48041.51</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>707422-102-CM25</t>
+          <t>2672-24-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5838.66</v>
+        <v>35693.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>652-207-CM25</t>
+          <t>707422-102-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>35183.55</v>
+        <v>5838.66</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2672-24-CM25</t>
+          <t>652-207-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>35693.5</v>
+        <v>35183.55</v>
       </c>
     </row>
     <row r="108">
@@ -7664,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2102-489-CM25</t>
+          <t>1070329-170-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>30437.46</v>
+        <v>13177.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1070329-170-CM25</t>
+          <t>2102-489-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>13177.1</v>
+        <v>30437.46</v>
       </c>
     </row>
     <row r="114">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3220-435-CM25</t>
+          <t>1057541-518-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>19711.02</v>
+        <v>1011.84</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3361-39-CM25</t>
+          <t>3220-435-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>302.4</v>
+        <v>19711.02</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057541-518-CM25</t>
+          <t>3361-39-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1011.84</v>
+        <v>302.4</v>
       </c>
     </row>
     <row r="128">
@@ -8834,7 +8834,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3355-242-CM25</t>
+          <t>4358-182-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>20753.97</v>
+        <v>2050.83</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4358-182-CM25</t>
+          <t>933-80-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2050.83</v>
+        <v>212.67</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>933-80-CM25</t>
+          <t>933-81-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>212.67</v>
+        <v>478.74</v>
       </c>
     </row>
     <row r="133">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>933-81-CM25</t>
+          <t>3355-242-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>478.74</v>
+        <v>20753.97</v>
       </c>
     </row>
     <row r="135">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057540-16398-CM25</t>
+          <t>4375-2040-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>61246.2</v>
+        <v>10044.38</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4414-887-CM25</t>
+          <t>1057540-16398-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>12859.55</v>
+        <v>61246.2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4375-2040-CM25</t>
+          <t>4414-887-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,7 +9738,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10044.38</v>
+        <v>12859.55</v>
       </c>
     </row>
     <row r="144">
@@ -9874,7 +9874,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3355-267-CM25</t>
+          <t>4375-1984-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1608.92</v>
+        <v>8314.559999999999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4375-1984-CM25</t>
+          <t>3355-269-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8314.559999999999</v>
+        <v>2146.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3355-269-CM25</t>
+          <t>3355-267-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2146.2</v>
+        <v>1608.92</v>
       </c>
     </row>
     <row r="149">
@@ -10134,7 +10134,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3355-278-CM25</t>
+          <t>4083-321-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10154,17 +10154,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2961.74</v>
+        <v>3587.41</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4083-321-CM25</t>
+          <t>3355-278-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10219,17 +10219,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3587.41</v>
+        <v>2961.74</v>
       </c>
     </row>
     <row r="152">
@@ -11109,7 +11109,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3361-49-CM25</t>
+          <t>1070329-256-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>309.25</v>
+        <v>14450.41</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1070329-256-CM25</t>
+          <t>3361-49-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>14450.41</v>
+        <v>309.25</v>
       </c>
     </row>
     <row r="167">
@@ -11369,7 +11369,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4074-390-CM25</t>
+          <t>4074-389-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7069.91</v>
+        <v>18398.31</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4074-389-CM25</t>
+          <t>4074-390-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>18398.31</v>
+        <v>7069.91</v>
       </c>
     </row>
     <row r="171">
@@ -11564,7 +11564,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1057415-392-CM25</t>
+          <t>1057541-720-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>18633.16</v>
+        <v>53707.38</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1057541-720-CM25</t>
+          <t>1057415-392-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>53707.38</v>
+        <v>18633.16</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3355-355-CM25</t>
+          <t>3355-357-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2617.22</v>
+        <v>1256.27</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3355-357-CM25</t>
+          <t>3355-355-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1256.27</v>
+        <v>2617.22</v>
       </c>
     </row>
     <row r="176">
@@ -12669,7 +12669,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3355-405-CM25</t>
+          <t>3365-194-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2793.6</v>
+        <v>1544.45</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3365-194-CM25</t>
+          <t>3355-405-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1544.45</v>
+        <v>2793.6</v>
       </c>
     </row>
     <row r="191">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>707422-232-CM25</t>
+          <t>3365-211-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5078.22</v>
+        <v>776.64</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3365-211-CM25</t>
+          <t>707422-232-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>776.64</v>
+        <v>5078.22</v>
       </c>
     </row>
     <row r="217">
@@ -14554,7 +14554,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3355-453-CM25</t>
+          <t>1057420-868-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14579,12 +14579,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1260.88</v>
+        <v>18685.89</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1057420-868-CM25</t>
+          <t>3355-453-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>18685.89</v>
+        <v>1260.88</v>
       </c>
     </row>
     <row r="220">
@@ -14749,7 +14749,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3220-789-CM25</t>
+          <t>3355-468-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14808,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>24956.37</v>
+        <v>663.5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3355-468-CM25</t>
+          <t>3220-789-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14873,7 +14873,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>663.5</v>
+        <v>24956.37</v>
       </c>
     </row>
     <row r="223">
@@ -14944,7 +14944,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4034-948-CM25</t>
+          <t>1070329-373-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14964,17 +14964,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>423.13</v>
+        <v>13752.46</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1070329-373-CM25</t>
+          <t>4034-948-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15029,17 +15029,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>13752.46</v>
+        <v>423.13</v>
       </c>
     </row>
     <row r="226">
@@ -15854,7 +15854,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3355-502-CM25</t>
+          <t>3355-506-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1622.12</v>
+        <v>2138.8</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3355-506-CM25</t>
+          <t>3355-502-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2138.8</v>
+        <v>1622.12</v>
       </c>
     </row>
     <row r="240">
@@ -16374,7 +16374,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>973168-19-CM25</t>
+          <t>973168-18-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1043.68</v>
+        <v>739.27</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>973168-18-CM25</t>
+          <t>973168-19-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>739.27</v>
+        <v>1043.68</v>
       </c>
     </row>
     <row r="248">
@@ -16829,7 +16829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>995118-165-CM25</t>
+          <t>1070329-432-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2963.03</v>
+        <v>13836.91</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3220-911-CM25</t>
+          <t>995118-165-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>25508.05</v>
+        <v>2963.03</v>
       </c>
     </row>
     <row r="255">
@@ -17089,7 +17089,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1070329-432-CM25</t>
+          <t>3220-911-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>13836.91</v>
+        <v>25508.05</v>
       </c>
     </row>
     <row r="258">
@@ -17609,7 +17609,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4494-877-CM25</t>
+          <t>4494-875-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4814.82</v>
+        <v>10525.29</v>
       </c>
     </row>
     <row r="266">
@@ -17739,7 +17739,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4494-875-CM25</t>
+          <t>4494-877-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>10525.29</v>
+        <v>4814.82</v>
       </c>
     </row>
     <row r="268">
@@ -17869,7 +17869,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1057422-852-CM25</t>
+          <t>1349-163-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.002.019-4</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>20822.54</v>
+        <v>21452.03</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1349-163-CM25</t>
+          <t>1057422-852-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.002.019-4</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>21452.03</v>
+        <v>20822.54</v>
       </c>
     </row>
     <row r="271">
@@ -18974,7 +18974,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1057420-21-CM26</t>
+          <t>1057422-3-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>20349.1</v>
+        <v>70159.98</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1057422-3-CM26</t>
+          <t>1057420-21-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>70159.98</v>
+        <v>20349.1</v>
       </c>
     </row>
     <row r="288">
@@ -19494,7 +19494,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1070329-3-CM26</t>
+          <t>3220-14-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>14055.95</v>
+        <v>31176.16</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>3220-14-CM26</t>
+          <t>1070329-3-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19618,7 +19618,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>31176.16</v>
+        <v>14055.95</v>
       </c>
     </row>
     <row r="296">
@@ -19754,7 +19754,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1057540-272-CM26</t>
+          <t>3382-21-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>65.311.270-K</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19813,13 +19813,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>83046.8</v>
+        <v>1165.57</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3382-21-CM26</t>
+          <t>1057540-272-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>65.311.270-K</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1165.57</v>
+        <v>83046.8</v>
       </c>
     </row>
     <row r="300">
@@ -20144,7 +20144,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4462-85-CM26</t>
+          <t>1057415-2789-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,13 +20203,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1099.98</v>
+        <v>26974.01</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1057415-2789-CM26</t>
+          <t>4462-85-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>26974.01</v>
+        <v>1099.98</v>
       </c>
     </row>
     <row r="306">
@@ -21314,7 +21314,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1576-41-CM26</t>
+          <t>1576-42-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21373,13 +21373,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>57997.66</v>
+        <v>7448.05</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1576-42-CM26</t>
+          <t>1576-41-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21438,7 +21438,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>7448.05</v>
+        <v>57997.66</v>
       </c>
     </row>
     <row r="324">
@@ -21834,7 +21834,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4434-5-CM26</t>
+          <t>1057541-289-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21859,12 +21859,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>590.24</v>
+        <v>59236.33</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1057541-289-CM26</t>
+          <t>4434-5-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21958,13 +21958,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>59236.33</v>
+        <v>590.24</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1335445-12-CM26</t>
+          <t>707422-50-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2237.34</v>
+        <v>13504.41</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>707422-50-CM26</t>
+          <t>1335445-12-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>13504.41</v>
+        <v>2237.34</v>
       </c>
     </row>
     <row r="334">
@@ -23199,7 +23199,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4414-575-CM26</t>
+          <t>4414-578-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>14824.18</v>
+        <v>5413.14</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4414-578-CM26</t>
+          <t>4414-575-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23323,13 +23323,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>5413.14</v>
+        <v>14824.18</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>995118-60-CM26</t>
+          <t>1057414-340-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23354,12 +23354,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1128.22</v>
+        <v>4498.47</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1057414-340-CM26</t>
+          <t>995118-60-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23419,12 +23419,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23453,7 +23453,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>4498.47</v>
+        <v>1128.22</v>
       </c>
     </row>
     <row r="355">
@@ -23524,7 +23524,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1070329-135-CM26</t>
+          <t>652-146-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,13 +23583,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>13443.77</v>
+        <v>44148.6</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>652-146-CM26</t>
+          <t>1070329-135-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23614,12 +23614,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>44148.6</v>
+        <v>13443.77</v>
       </c>
     </row>
     <row r="358">
@@ -23979,7 +23979,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1057540-1431-CM26</t>
+          <t>4414-726-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -24004,12 +24004,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>79672.14</v>
+        <v>7704.88</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4414-726-CM26</t>
+          <t>1057540-1431-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24103,7 +24103,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>7704.88</v>
+        <v>79672.14</v>
       </c>
     </row>
     <row r="365">
@@ -24174,7 +24174,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>831-145-CM26</t>
+          <t>1057422-368-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2759.44</v>
+        <v>72368.35000000001</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1057422-368-CM26</t>
+          <t>831-145-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24264,12 +24264,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>72368.35000000001</v>
+        <v>2759.44</v>
       </c>
     </row>
     <row r="368">
@@ -24564,7 +24564,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2704-1164-CM26</t>
+          <t>4414-793-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24584,17 +24584,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24623,13 +24623,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>5727.5</v>
+        <v>393.06</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>4414-793-CM26</t>
+          <t>2704-1164-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24649,17 +24649,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>393.06</v>
+        <v>5727.5</v>
       </c>
     </row>
     <row r="374">
@@ -25019,7 +25019,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>4491-323-CM26</t>
+          <t>4491-322-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -25078,13 +25078,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>5224.04</v>
+        <v>6791.41</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>4491-322-CM26</t>
+          <t>4491-323-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -25143,7 +25143,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>6791.41</v>
+        <v>5224.04</v>
       </c>
     </row>
     <row r="381">
@@ -25474,7 +25474,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1057422-511-CM26</t>
+          <t>4359-133-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25494,17 +25494,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>232.15</v>
+        <v>2348.79</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>4359-133-CM26</t>
+          <t>2102-606-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25559,17 +25559,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,13 +25598,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2348.79</v>
+        <v>46907.15</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2102-606-CM26</t>
+          <t>1057422-511-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25629,12 +25629,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25663,7 +25663,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>46907.15</v>
+        <v>232.15</v>
       </c>
     </row>
     <row r="389">
@@ -25799,7 +25799,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>554892-5-CM26</t>
+          <t>4360-71-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25824,12 +25824,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25858,13 +25858,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1414.11</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4360-71-CM26</t>
+          <t>554892-5-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25889,12 +25889,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25923,7 +25923,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>24.66</v>
+        <v>1414.11</v>
       </c>
     </row>
     <row r="393">
@@ -26124,7 +26124,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>3319-276-CM26</t>
+          <t>1057540-1942-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26164,12 +26164,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -26183,13 +26183,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>33842.74</v>
+        <v>79468.91</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1057540-1942-CM26</t>
+          <t>3319-276-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26214,12 +26214,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26229,12 +26229,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -26248,7 +26248,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>79468.91</v>
+        <v>33842.74</v>
       </c>
     </row>
     <row r="398">
@@ -26319,7 +26319,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1057415-3113-CM26</t>
+          <t>4359-159-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26344,12 +26344,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,13 +26378,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>32580.79</v>
+        <v>2334.24</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>831-241-CM26</t>
+          <t>1057415-3113-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26404,17 +26404,17 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26443,13 +26443,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1750.81</v>
+        <v>32580.79</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4359-159-CM26</t>
+          <t>831-241-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26469,17 +26469,17 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>2334.24</v>
+        <v>1750.81</v>
       </c>
     </row>
     <row r="402">
@@ -26839,7 +26839,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>4351-384-CM26</t>
+          <t>2416-226-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26859,17 +26859,17 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26898,13 +26898,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>16874.04</v>
+        <v>32533.73</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2416-226-CM26</t>
+          <t>4351-384-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26924,17 +26924,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26963,13 +26963,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>32533.73</v>
+        <v>16874.04</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>831-279-CM26</t>
+          <t>652-251-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26989,17 +26989,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,13 +27028,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1676.16</v>
+        <v>47157.71</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>652-251-CM26</t>
+          <t>831-279-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27054,17 +27054,17 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>47157.71</v>
+        <v>1676.16</v>
       </c>
     </row>
     <row r="411">
@@ -27229,7 +27229,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2410-443-CM26</t>
+          <t>972135-11-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27249,17 +27249,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,13 +27288,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>16737.44</v>
+        <v>15787.98</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>972135-11-CM26</t>
+          <t>2410-443-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27314,17 +27314,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>15787.98</v>
+        <v>16737.44</v>
       </c>
     </row>
     <row r="415">
@@ -27424,7 +27424,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2078-1039-CM26</t>
+          <t>4363-10-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27449,12 +27449,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1003.35</v>
+        <v>7615.23</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>4363-10-CM26</t>
+          <t>2078-1039-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27514,12 +27514,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>7615.23</v>
+        <v>1003.35</v>
       </c>
     </row>
     <row r="418">
@@ -27944,7 +27944,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1079576-994-CM26</t>
+          <t>995118-133-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -28003,13 +28003,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>313.31</v>
+        <v>218</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>995118-133-CM26</t>
+          <t>1079576-994-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28029,7 +28029,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>218</v>
+        <v>313.31</v>
       </c>
     </row>
     <row r="426">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -28334,7 +28334,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>707422-171-CM26</t>
+          <t>1070329-276-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28354,17 +28354,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28393,13 +28393,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1073.42</v>
+        <v>14728.76</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1070329-276-CM26</t>
+          <t>707422-171-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28424,12 +28424,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -28458,7 +28458,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>14728.76</v>
+        <v>1073.42</v>
       </c>
     </row>
     <row r="432">
@@ -28484,7 +28484,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -28529,7 +28529,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>4375-2536-CM26</t>
+          <t>4474-937-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -28588,13 +28588,13 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>42978.38</v>
+        <v>206.09</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>4474-937-CM26</t>
+          <t>4375-2536-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -28614,46 +28614,826 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>61.602.189-3</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>42978.38</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>707422-179-CM26</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>5684.81</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>1057540-2421-CM26</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>61.602.198-2</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>75946.23</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1057430-2782-CM26</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>69.160.600-7</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M434" s="2" t="n">
-        <v>206.09</v>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>61.602.203-2</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LOTA</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>1807.52</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>976780-11-CM26</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>69.160.100-5</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>687.13</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>1057415-3239-CM26</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>61.602.220-2</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="n">
+        <v>30310.76</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>995118-151-CM26</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>61.954.400-5</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>353.42</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>1057541-896-CM26</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>61.607.200-5</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M441" s="2" t="n">
+        <v>1763.88</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>3945-731-CM26</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>69.160.400-4</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M442" s="2" t="n">
+        <v>15462.83</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2362-99-CM26</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>69.150.800-5</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M443" s="2" t="n">
+        <v>1809.22</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>1057431-3253-CM26</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>61.602.295-4</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M444" s="2" t="n">
+        <v>8790.9</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2078-1173-CM26</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M445" s="2" t="n">
+        <v>28244.57</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2408-1070-CM26</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="n">
+        <v>27921.64</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/biobio.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M447"/>
+  <dimension ref="A1:M450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2074,7 +2074,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057418-98-CM25</t>
+          <t>1057540-6539-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.302-8</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE MULCHEN</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20064.79</v>
+        <v>72179.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057540-6539-CM25</t>
+          <t>1057418-98-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.607.302-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE MULCHEN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>72179.67</v>
+        <v>20064.79</v>
       </c>
     </row>
     <row r="28">
@@ -2594,7 +2594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1070329-62-CM25</t>
+          <t>3365-21-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>13571.03</v>
+        <v>2115.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3365-21-CM25</t>
+          <t>4434-7-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2115.07</v>
+        <v>1032.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4434-7-CM25</t>
+          <t>1070329-62-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1032.87</v>
+        <v>13571.03</v>
       </c>
     </row>
     <row r="37">
@@ -2984,7 +2984,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2421-2813-CM25</t>
+          <t>654-58-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3004,17 +3004,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5236.54</v>
+        <v>3098.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>654-58-CM25</t>
+          <t>2421-2813-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3098.66</v>
+        <v>5236.54</v>
       </c>
     </row>
     <row r="42">
@@ -3309,7 +3309,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3365-42-CM25</t>
+          <t>1057422-142-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3221.89</v>
+        <v>16523.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057422-142-CM25</t>
+          <t>3365-42-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>16523.41</v>
+        <v>3221.89</v>
       </c>
     </row>
     <row r="47">
@@ -3569,7 +3569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3355-89-CM25</t>
+          <t>3355-94-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2010.21</v>
+        <v>2127.21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3355-94-CM25</t>
+          <t>3355-89-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2127.21</v>
+        <v>2010.21</v>
       </c>
     </row>
     <row r="51">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1576-41-CM25</t>
+          <t>652-104-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8549.129999999999</v>
+        <v>26151.79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>652-104-CM25</t>
+          <t>1576-41-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4109,17 +4109,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>26151.79</v>
+        <v>8549.129999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1070329-95-CM25</t>
+          <t>2102-278-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>12155.77</v>
+        <v>26113.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2102-278-CM25</t>
+          <t>1070329-95-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>26113.6</v>
+        <v>12155.77</v>
       </c>
     </row>
     <row r="60">
@@ -5064,7 +5064,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3355-146-CM25</t>
+          <t>1057420-316-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1238.12</v>
+        <v>17981.61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1057420-316-CM25</t>
+          <t>3355-146-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>17981.61</v>
+        <v>1238.12</v>
       </c>
     </row>
     <row r="74">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2102-371-CM25</t>
+          <t>652-145-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>25372.55</v>
+        <v>32973.85</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>652-145-CM25</t>
+          <t>2102-371-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>32973.85</v>
+        <v>25372.55</v>
       </c>
     </row>
     <row r="81">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4362-24-CM25</t>
+          <t>1057541-409-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>20781.98</v>
+        <v>2018.66</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057541-409-CM25</t>
+          <t>4362-24-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2018.66</v>
+        <v>20781.98</v>
       </c>
     </row>
     <row r="91">
@@ -6689,7 +6689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>995118-60-CM25</t>
+          <t>1057414-284-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4854.01</v>
+        <v>340.63</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057420-416-CM25</t>
+          <t>1057414-281-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>20554.7</v>
+        <v>425.79</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057414-281-CM25</t>
+          <t>2101-2369-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6839,17 +6839,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.602.213-k</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>HOSPITAL INTERCULTURAL KALLVU LLANKA.-</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>425.79</v>
+        <v>5254.23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057414-284-CM25</t>
+          <t>1057420-416-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>340.63</v>
+        <v>20554.7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2101-2369-CM25</t>
+          <t>995118-60-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.602.213-k</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL INTERCULTURAL KALLVU LLANKA.-</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5254.23</v>
+        <v>4854.01</v>
       </c>
     </row>
     <row r="102">
@@ -7144,7 +7144,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3319-105-CM25</t>
+          <t>4358-140-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>48041.51</v>
+        <v>6315.87</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4358-140-CM25</t>
+          <t>3355-205-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6315.87</v>
+        <v>1068.11</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3355-205-CM25</t>
+          <t>3319-105-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1068.11</v>
+        <v>48041.51</v>
       </c>
     </row>
     <row r="107">
@@ -7794,7 +7794,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2102-489-CM25</t>
+          <t>1070329-170-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>30437.46</v>
+        <v>13177.1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1070329-170-CM25</t>
+          <t>2102-489-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>13177.1</v>
+        <v>30437.46</v>
       </c>
     </row>
     <row r="116">
@@ -8379,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1057415-285-CM25</t>
+          <t>1057422-367-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>23050.08</v>
+        <v>19884.22</v>
       </c>
     </row>
     <row r="124">
@@ -8574,7 +8574,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057422-367-CM25</t>
+          <t>1057415-285-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>19884.22</v>
+        <v>23050.08</v>
       </c>
     </row>
     <row r="127">
@@ -8964,7 +8964,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>933-80-CM25</t>
+          <t>4358-182-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>212.67</v>
+        <v>2050.83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>933-81-CM25</t>
+          <t>933-80-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>478.74</v>
+        <v>212.67</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3355-242-CM25</t>
+          <t>933-81-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>20753.97</v>
+        <v>478.74</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4358-182-CM25</t>
+          <t>995118-78-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2050.83</v>
+        <v>3957.11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>995118-78-CM25</t>
+          <t>3355-242-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3957.11</v>
+        <v>20753.97</v>
       </c>
     </row>
     <row r="137">
@@ -9354,7 +9354,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3365-128-CM25</t>
+          <t>1057541-560-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2111.87</v>
+        <v>278.77</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1057541-560-CM25</t>
+          <t>3365-128-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>278.77</v>
+        <v>2111.87</v>
       </c>
     </row>
     <row r="140">
@@ -10069,7 +10069,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3355-267-CM25</t>
+          <t>3355-269-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1608.92</v>
+        <v>2146.2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3355-269-CM25</t>
+          <t>3355-267-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2146.2</v>
+        <v>1608.92</v>
       </c>
     </row>
     <row r="151">
@@ -10979,7 +10979,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>652-305-CM25</t>
+          <t>4491-352-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10999,17 +10999,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.150.501-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>31850.81</v>
+        <v>4471.52</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4491-352-CM25</t>
+          <t>652-305-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11064,17 +11064,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>4471.52</v>
+        <v>31850.81</v>
       </c>
     </row>
     <row r="165">
@@ -11239,7 +11239,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3361-49-CM25</t>
+          <t>1070329-256-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>309.25</v>
+        <v>14450.41</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1070329-256-CM25</t>
+          <t>3361-49-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>14450.41</v>
+        <v>309.25</v>
       </c>
     </row>
     <row r="169">
@@ -11694,7 +11694,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1057415-392-CM25</t>
+          <t>1057541-720-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>18633.16</v>
+        <v>53707.38</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057541-720-CM25</t>
+          <t>1057415-392-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>53707.38</v>
+        <v>18633.16</v>
       </c>
     </row>
     <row r="176">
@@ -14034,7 +14034,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1057540-17174-CM25</t>
+          <t>1375757-69-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14093,13 +14093,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>73980.62</v>
+        <v>8388</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1375757-69-CM25</t>
+          <t>1057540-17174-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14124,12 +14124,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14158,7 +14158,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8388</v>
+        <v>73980.62</v>
       </c>
     </row>
     <row r="212">
@@ -14489,7 +14489,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>707422-232-CM25</t>
+          <t>3365-211-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5078.22</v>
+        <v>776.64</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>995118-148-CM25</t>
+          <t>707422-232-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,17 +14574,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1867.59</v>
+        <v>5078.22</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3365-211-CM25</t>
+          <t>995118-148-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>776.64</v>
+        <v>1867.59</v>
       </c>
     </row>
     <row r="220">
@@ -15074,7 +15074,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4034-948-CM25</t>
+          <t>1070329-373-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15094,17 +15094,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>423.13</v>
+        <v>13752.46</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1070329-373-CM25</t>
+          <t>4034-948-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15159,17 +15159,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>13752.46</v>
+        <v>423.13</v>
       </c>
     </row>
     <row r="228">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3361-72-CM25</t>
+          <t>696228-152-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>372.13</v>
+        <v>9119.01</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>696228-152-CM25</t>
+          <t>3361-72-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15744,17 +15744,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>9119.01</v>
+        <v>372.13</v>
       </c>
     </row>
     <row r="237">
@@ -16569,7 +16569,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>973168-20-CM25</t>
+          <t>973168-19-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>478.35</v>
+        <v>1043.68</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>973168-19-CM25</t>
+          <t>973168-20-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1043.68</v>
+        <v>478.35</v>
       </c>
     </row>
     <row r="251">
@@ -16764,7 +16764,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1057420-980-CM25</t>
+          <t>891-61-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>21401.93</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>891-61-CM25</t>
+          <t>1057420-980-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>56.67</v>
+        <v>21401.93</v>
       </c>
     </row>
     <row r="254">
@@ -16959,7 +16959,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>995118-165-CM25</t>
+          <t>652-485-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2963.03</v>
+        <v>40300.46</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3220-911-CM25</t>
+          <t>3355-532-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>25508.05</v>
+        <v>1708.56</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>652-485-CM25</t>
+          <t>1070329-432-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>40300.46</v>
+        <v>13836.91</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3355-532-CM25</t>
+          <t>3220-911-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1708.56</v>
+        <v>25508.05</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1070329-432-CM25</t>
+          <t>995118-165-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>13836.91</v>
+        <v>2963.03</v>
       </c>
     </row>
     <row r="260">
@@ -17739,7 +17739,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4494-871-CM25</t>
+          <t>4494-875-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>12752.82</v>
+        <v>10525.29</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4494-877-CM25</t>
+          <t>4494-871-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4814.82</v>
+        <v>12752.82</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>4494-875-CM25</t>
+          <t>4494-877-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>10525.29</v>
+        <v>4814.82</v>
       </c>
     </row>
     <row r="270">
@@ -19429,7 +19429,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3355-10-CM26</t>
+          <t>3355-9-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19488,13 +19488,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1125.84</v>
+        <v>2812.7</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3355-9-CM26</t>
+          <t>3355-10-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2812.7</v>
+        <v>1125.84</v>
       </c>
     </row>
     <row r="295">
@@ -19624,7 +19624,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3220-14-CM26</t>
+          <t>1070329-3-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19649,12 +19649,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>31176.16</v>
+        <v>14055.95</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1070329-3-CM26</t>
+          <t>3220-14-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>14055.95</v>
+        <v>31176.16</v>
       </c>
     </row>
     <row r="298">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3382-21-CM26</t>
+          <t>1057540-272-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>65.311.270-K</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1165.57</v>
+        <v>83046.8</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1057540-272-CM26</t>
+          <t>3382-21-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>65.311.270-K</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>83046.8</v>
+        <v>1165.57</v>
       </c>
     </row>
     <row r="302">
@@ -20079,7 +20079,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4074-3-CM26</t>
+          <t>4074-4-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>7698.53</v>
+        <v>2311.87</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4074-4-CM26</t>
+          <t>4074-3-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2311.87</v>
+        <v>7698.53</v>
       </c>
     </row>
     <row r="305">
@@ -20274,7 +20274,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4462-85-CM26</t>
+          <t>1057415-2789-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1099.98</v>
+        <v>26974.01</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1057415-2789-CM26</t>
+          <t>4462-85-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>26974.01</v>
+        <v>1099.98</v>
       </c>
     </row>
     <row r="308">
@@ -20794,7 +20794,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1057415-2819-CM26</t>
+          <t>1057541-213-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>30229.91</v>
+        <v>35004.33</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1057541-213-CM26</t>
+          <t>1057415-2819-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20918,7 +20918,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>35004.33</v>
+        <v>30229.91</v>
       </c>
     </row>
     <row r="316">
@@ -21639,7 +21639,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2102-242-CM26</t>
+          <t>3365-36-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21664,12 +21664,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>40530.29</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3365-36-CM26</t>
+          <t>2102-242-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21763,7 +21763,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2683.64</v>
+        <v>40530.29</v>
       </c>
     </row>
     <row r="329">
@@ -22289,7 +22289,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1057415-2882-CM26</t>
+          <t>1057422-238-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>24322.83</v>
+        <v>72079.69</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1057422-238-CM26</t>
+          <t>1057415-2882-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>72079.69</v>
+        <v>24322.83</v>
       </c>
     </row>
     <row r="339">
@@ -22549,7 +22549,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>707422-56-CM26</t>
+          <t>4238-82-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22574,12 +22574,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22608,13 +22608,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>5861.08</v>
+        <v>31230.26</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4238-82-CM26</t>
+          <t>707422-56-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>31230.26</v>
+        <v>5861.08</v>
       </c>
     </row>
     <row r="343">
@@ -23134,7 +23134,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1057541-390-CM26</t>
+          <t>707422-68-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23159,12 +23159,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23193,13 +23193,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>56374.97</v>
+        <v>11835.83</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>707422-68-CM26</t>
+          <t>1057541-390-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>11835.83</v>
+        <v>56374.97</v>
       </c>
     </row>
     <row r="352">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>995118-60-CM26</t>
+          <t>1057414-340-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1128.22</v>
+        <v>4498.47</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1057414-340-CM26</t>
+          <t>995118-60-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>4498.47</v>
+        <v>1128.22</v>
       </c>
     </row>
     <row r="357">
@@ -23654,7 +23654,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1070329-135-CM26</t>
+          <t>652-146-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>13443.77</v>
+        <v>44148.6</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>652-146-CM26</t>
+          <t>1070329-135-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23744,12 +23744,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>44148.6</v>
+        <v>13443.77</v>
       </c>
     </row>
     <row r="360">
@@ -25539,7 +25539,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1057422-511-CM26</t>
+          <t>4359-133-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,7 +25598,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>232.15</v>
+        <v>2348.79</v>
       </c>
     </row>
     <row r="388">
@@ -25669,7 +25669,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>4359-133-CM26</t>
+          <t>1057422-511-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25694,12 +25694,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25728,13 +25728,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2348.79</v>
+        <v>232.15</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>652-201-CM26</t>
+          <t>973168-5-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>41904.55</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>973168-5-CM26</t>
+          <t>652-201-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25824,12 +25824,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>214.4</v>
+        <v>41904.55</v>
       </c>
     </row>
     <row r="392">
@@ -26384,7 +26384,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1057415-3113-CM26</t>
+          <t>4359-159-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26409,12 +26409,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26443,13 +26443,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>32580.79</v>
+        <v>2334.24</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>831-241-CM26</t>
+          <t>1057415-3113-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26474,12 +26474,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26508,13 +26508,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1750.81</v>
+        <v>32580.79</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4359-159-CM26</t>
+          <t>831-241-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26539,12 +26539,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26573,7 +26573,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2334.24</v>
+        <v>1750.81</v>
       </c>
     </row>
     <row r="403">
@@ -27164,7 +27164,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1070329-235-CM26</t>
+          <t>2102-735-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>15141.93</v>
+        <v>50557.56</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2102-735-CM26</t>
+          <t>1070329-235-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,12 +27254,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,13 +27288,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>50557.56</v>
+        <v>15141.93</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>972135-11-CM26</t>
+          <t>2410-443-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,12 +27319,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>15787.98</v>
+        <v>16737.44</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2410-443-CM26</t>
+          <t>972135-11-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>16737.44</v>
+        <v>15787.98</v>
       </c>
     </row>
     <row r="416">
@@ -27749,7 +27749,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1057422-631-CM26</t>
+          <t>4650-126-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>71362.78999999999</v>
+        <v>4628.84</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>4650-126-CM26</t>
+          <t>1057422-631-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27839,12 +27839,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27873,7 +27873,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>4628.84</v>
+        <v>71362.78999999999</v>
       </c>
     </row>
     <row r="423">
@@ -28594,7 +28594,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>4375-2536-CM26</t>
+          <t>4474-937-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -28614,17 +28614,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -28653,13 +28653,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>42978.38</v>
+        <v>206.09</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>4474-937-CM26</t>
+          <t>4375-2536-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28679,17 +28679,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -28718,7 +28718,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>206.09</v>
+        <v>42978.38</v>
       </c>
     </row>
     <row r="436">
@@ -28789,7 +28789,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>976780-11-CM26</t>
+          <t>1057540-2421-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28809,17 +28809,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -28848,7 +28848,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>687.13</v>
+        <v>75946.23</v>
       </c>
     </row>
     <row r="438">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -28919,7 +28919,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1057540-2421-CM26</t>
+          <t>976780-11-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28939,17 +28939,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,7 +28978,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>75946.23</v>
+        <v>687.13</v>
       </c>
     </row>
     <row r="440">
@@ -29114,7 +29114,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>3945-731-CM26</t>
+          <t>1057541-896-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -29139,12 +29139,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -29154,12 +29154,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -29173,13 +29173,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>15462.83</v>
+        <v>1763.88</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1057541-896-CM26</t>
+          <t>3945-731-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -29204,12 +29204,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -29219,12 +29219,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -29238,7 +29238,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1763.88</v>
+        <v>15462.83</v>
       </c>
     </row>
     <row r="444">
@@ -29499,6 +29499,201 @@
       </c>
       <c r="M447" s="2" t="n">
         <v>28244.57</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2410-504-CM26</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>69.170.102-6</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M448" s="2" t="n">
+        <v>24839.65</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1070329-340-CM26</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>61.980.370-1</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>CESFAM LIRQUEN</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M449" s="2" t="n">
+        <v>13684.75</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>652-380-CM26</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>61.954.500-1</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M450" s="2" t="n">
+        <v>42246.82</v>
       </c>
     </row>
   </sheetData>
